--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NEW_JERSEY_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NEW_JERSEY_2015.xlsx
@@ -805,7 +805,7 @@
         <v>19</v>
       </c>
       <c r="D25">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="26">
@@ -931,7 +931,7 @@
         <v>19</v>
       </c>
       <c r="D32">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="33">
@@ -1075,7 +1075,7 @@
         <v>19</v>
       </c>
       <c r="D40">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="41">
@@ -1111,7 +1111,7 @@
         <v>19</v>
       </c>
       <c r="D42">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="43">
@@ -2641,7 +2641,7 @@
         <v>18</v>
       </c>
       <c r="D127">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="128">
@@ -3469,7 +3469,7 @@
         <v>178</v>
       </c>
       <c r="D173">
-        <v>0.009036450401055945</v>
+        <v>0.009036450401055943</v>
       </c>
     </row>
     <row r="174">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C230">
@@ -5053,7 +5053,7 @@
         <v>19</v>
       </c>
       <c r="D261">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="262">
@@ -5125,7 +5125,7 @@
         <v>18</v>
       </c>
       <c r="D265">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="266">
@@ -5665,7 +5665,7 @@
         <v>18</v>
       </c>
       <c r="D295">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="296">
@@ -5701,7 +5701,7 @@
         <v>18</v>
       </c>
       <c r="D297">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="298">
@@ -9409,7 +9409,7 @@
         <v>19</v>
       </c>
       <c r="D503">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="504">
@@ -9517,7 +9517,7 @@
         <v>18</v>
       </c>
       <c r="D509">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="510">
@@ -10561,7 +10561,7 @@
         <v>19</v>
       </c>
       <c r="D567">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="568">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C680">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C681">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C742">
@@ -14161,7 +14161,7 @@
         <v>18</v>
       </c>
       <c r="D767">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="768">
@@ -14845,7 +14845,7 @@
         <v>19</v>
       </c>
       <c r="D805">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="806">
@@ -14917,7 +14917,7 @@
         <v>19</v>
       </c>
       <c r="D809">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="810">
@@ -15295,7 +15295,7 @@
         <v>18</v>
       </c>
       <c r="D830">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="831">
@@ -15439,7 +15439,7 @@
         <v>19</v>
       </c>
       <c r="D838">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="839">
@@ -16249,7 +16249,7 @@
         <v>18</v>
       </c>
       <c r="D883">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="884">
@@ -16429,7 +16429,7 @@
         <v>18</v>
       </c>
       <c r="D893">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="894">
@@ -16537,7 +16537,7 @@
         <v>19</v>
       </c>
       <c r="D899">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="900">
@@ -17077,7 +17077,7 @@
         <v>19</v>
       </c>
       <c r="D929">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="930">
@@ -17473,7 +17473,7 @@
         <v>18</v>
       </c>
       <c r="D951">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="952">
@@ -17617,7 +17617,7 @@
         <v>18</v>
       </c>
       <c r="D959">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="960">
@@ -18049,7 +18049,7 @@
         <v>196</v>
       </c>
       <c r="D983">
-        <v>0.009950248756218905</v>
+        <v>0.009950248756218904</v>
       </c>
     </row>
     <row r="984">
@@ -19129,7 +19129,7 @@
         <v>18</v>
       </c>
       <c r="D1043">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="1044">
@@ -19435,7 +19435,7 @@
         <v>196</v>
       </c>
       <c r="D1060">
-        <v>0.009950248756218905</v>
+        <v>0.009950248756218904</v>
       </c>
     </row>
     <row r="1061">
@@ -20893,7 +20893,7 @@
         <v>18</v>
       </c>
       <c r="D1141">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="1142">
@@ -21847,7 +21847,7 @@
         <v>19</v>
       </c>
       <c r="D1194">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="1195">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1207">
@@ -22585,7 +22585,7 @@
         <v>19</v>
       </c>
       <c r="D1235">
-        <v>0.0009645649304497919</v>
+        <v>0.000964564930449792</v>
       </c>
     </row>
     <row r="1236">
@@ -24223,7 +24223,7 @@
         <v>18</v>
       </c>
       <c r="D1326">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
     <row r="1327">
@@ -24871,7 +24871,7 @@
         <v>18</v>
       </c>
       <c r="D1362">
-        <v>0.0009137983551629607</v>
+        <v>0.0009137983551629608</v>
       </c>
     </row>
   </sheetData>
